--- a/consent_forms/024_summer_school_agreement_form--consent_forms.xlsx
+++ b/consent_forms/024_summer_school_agreement_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>summer_school_agreement_form</t>
+          <t>page1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>terms_and_conditions</t>
+          <t>Terms and Conditions</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>page2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Name (Student)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>page3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email (Student)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>page4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Phone (Student)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>page5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>Start Date</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>page6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>start_time</t>
+          <t>Start Time</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,40 +653,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>school_terms</t>
+          <t>page7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>terms_and_conditions</t>
+          <t>Authorized Person</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>submission_date</t>
+          <t>page8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>submission_date</t>
+          <t>Authorized Person Signature</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>submission_time</t>
+          <t>page9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>submission_time</t>
+          <t>Submitter Signature</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>name_authorized_rep</t>
+          <t>page10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>name_of_authorized_person</t>
+          <t>Name (Submitter)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>authorized_title</t>
+          <t>page11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>title_of_authorized_person</t>
+          <t>Title (Submitter)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>authorized_phone</t>
+          <t>page12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>phone_of_authorized_person</t>
+          <t>Phone (Submitter)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>authorized_email</t>
+          <t>page13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>email_of_authorized_person</t>
+          <t>Email (Submitter)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>authorized_date</t>
+          <t>page14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>date_of_authorized_person</t>
+          <t>Date (Submitter)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>authorized_time</t>
+          <t>page15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>time_of_authorized_person</t>
+          <t>Time (Submitter)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,40 +860,40 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>submitter_signature</t>
+          <t>page16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>submitter_signature</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>authorized_signature</t>
+          <t>page17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>authorized_person_signature</t>
+          <t>Agree to Terms and Conditions</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>submitter_name</t>
+          <t>page18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Authorized Person Notes</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>submitter_title</t>
+          <t>page19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>Additional Notes</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,23 +952,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>submitter_phone</t>
+          <t>page20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Page20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>submitter_email</t>
+          <t>page21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Page21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -998,17 +998,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>submitter_date</t>
+          <t>page22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Page22</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1021,17 +1021,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>submitter_time</t>
+          <t>page23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Page23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1044,17 +1044,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>submitter_notes</t>
+          <t>page24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Page24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1067,23 +1067,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>submitter_agreed</t>
+          <t>page25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>agree_to_terms</t>
+          <t>Page25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1101,9 +1101,9 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,7 +1126,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>name_authorized_rep_choices</t>
+          <t>page17_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>name_authorized_rep_choices</t>
+          <t>page17_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,34 +1160,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>submitter_agreed_choices</t>
+          <t>page20_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>authorized_person</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Authorized Person</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>submitter_agreed_choices</t>
+          <t>page20_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>submitter</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Submitter</t>
         </is>
       </c>
     </row>
